--- a/Result/profitability/7747.xlsx
+++ b/Result/profitability/7747.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM13"/>
+  <dimension ref="A1:AM14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1585,23 +1585,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="D10" t="n">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="E10" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F10" t="n">
-        <v>14.69</v>
+        <v>15.73</v>
       </c>
       <c r="G10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.80%</t>
+          <t>7.62%</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1620,13 +1620,13 @@
         <v>1.07375</v>
       </c>
       <c r="N10" t="n">
-        <v>16.555</v>
+        <v>16.685</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1653,10 +1653,10 @@
         <v>-0.256</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.8399999999999999</v>
+        <v>0.2000000000000011</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.05408886027044424</v>
+        <v>0.0128783000643915</v>
       </c>
       <c r="AA10" t="n">
         <v>-0.01999999999999991</v>
@@ -1665,10 +1665,10 @@
         <v>-0.02105263157894732</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.15</v>
+        <v>-0.1099999999999994</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.07260101010101017</v>
+        <v>-0.00694444444444442</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1712,23 +1712,23 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="D11" t="n">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>14.66</v>
+        <v>13.47</v>
       </c>
       <c r="G11" t="n">
         <v>24</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>7.01%</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1747,13 +1747,13 @@
         <v>1.05625</v>
       </c>
       <c r="N11" t="n">
-        <v>16.1425</v>
+        <v>16.12375</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1780,10 +1780,10 @@
         <v>-0.07526881720430112</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.02999999999999936</v>
+        <v>-2.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.0020422055820285</v>
+        <v>-0.1436745073108709</v>
       </c>
       <c r="AA11" t="n">
         <v>-0.2999999999999999</v>
@@ -1792,10 +1792,10 @@
         <v>-0.2586206896551724</v>
       </c>
       <c r="AC11" t="n">
-        <v>-1.699999999999999</v>
+        <v>-2.889999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.1039119804400978</v>
+        <v>-0.1766503667481661</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1874,7 +1874,7 @@
         <v>1.04375</v>
       </c>
       <c r="N12" t="n">
-        <v>15.47625</v>
+        <v>15.4575</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1907,10 +1907,10 @@
         <v>0.2790697674418605</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.5</v>
+        <v>0.6899999999999995</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.03410641200545705</v>
+        <v>0.05122494432071267</v>
       </c>
       <c r="AA12" t="n">
         <v>0.08000000000000007</v>
@@ -1931,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>1.0825</v>
       </c>
       <c r="N13" t="n">
-        <v>15.125</v>
+        <v>15.10625</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -2079,6 +2079,133 @@
       </c>
       <c r="AM13" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>7747</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>435</v>
+      </c>
+      <c r="D14" t="n">
+        <v>364</v>
+      </c>
+      <c r="E14" t="n">
+        <v>70</v>
+      </c>
+      <c r="F14" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="G14" t="n">
+        <v>49</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>11.18%</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>52</v>
+      </c>
+      <c r="K14" t="n">
+        <v>45</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.14875</v>
+      </c>
+      <c r="N14" t="n">
+        <v>15.145</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.09000000000000008</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.06474820143884896</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.9599999999999991</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.06319947333772213</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.5913978494623655</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.4199999999999982</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.02670057215511745</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK14" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
